--- a/fig2/FIG 2.xlsx
+++ b/fig2/FIG 2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="13284" activeTab="4"/>
+    <workbookView windowWidth="14940" windowHeight="13344" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="FIG 2B" sheetId="8" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="FIG 2M" sheetId="5" r:id="rId7"/>
     <sheet name="FIG 2N" sheetId="6" r:id="rId8"/>
     <sheet name="FIG 2O" sheetId="7" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1764,6 +1765,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -5047,7 +5059,7 @@
         <v>71900</v>
       </c>
       <c r="B2" s="1">
-        <v>26.1</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5055,7 +5067,7 @@
         <v>15500</v>
       </c>
       <c r="B3" s="1">
-        <v>5.23</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5063,7 +5075,7 @@
         <v>6100</v>
       </c>
       <c r="B4" s="1">
-        <v>17.7</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5071,7 +5083,7 @@
         <v>10000</v>
       </c>
       <c r="B5" s="1">
-        <v>1.33</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5079,7 +5091,7 @@
         <v>468000</v>
       </c>
       <c r="B6" s="1">
-        <v>35.1</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5087,7 +5099,7 @@
         <v>680000</v>
       </c>
       <c r="B7" s="1">
-        <v>32.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5095,7 +5107,7 @@
         <v>11600</v>
       </c>
       <c r="B8" s="1">
-        <v>0.42</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5103,7 +5115,7 @@
         <v>82900</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="15" spans="1:2">
